--- a/samples/corpus/full/entreprise/crew-schedule/2026-04-03_planning-des-equipes-s15-s17.xlsx
+++ b/samples/corpus/full/entreprise/crew-schedule/2026-04-03_planning-des-equipes-s15-s17.xlsx
@@ -739,7 +739,7 @@
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>Levée de la réserve R02 : reprise du nez de balcon du 3e étage</t>
+          <t>Levée de la réserve R02 : reprise du nez de balcon du 3e étage depuis la nacelle MAT-04</t>
         </is>
       </c>
     </row>
